--- a/光伏配储项目/电价数据/2026/茅湖站.xlsx
+++ b/光伏配储项目/电价数据/2026/茅湖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.6037899999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.67962</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6078600000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5922000000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5932500000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46952</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43977</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43203</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4372799999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45593</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5174800000000001</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.19935</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22051</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21499</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20089</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25266</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06219</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24297</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24585</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.90616</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.22333</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52063</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.52589</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60551</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60585</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72623</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21379</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.78178</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6546000000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.93337</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53869</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27484</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39067</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14281</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24362</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34944</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.51278</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.5128200000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75319</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8049299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.31263</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.1204</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86576</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79361</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75358</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51442</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47675</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46451</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41442</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70048</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74577</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8628400000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9037000000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48927</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5072099999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49708</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46233</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.70064</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55661</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.65979</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50961</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58196</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85697</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58357</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9361499999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8903099999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.56004</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8415900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.25029</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0574</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50273</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58704</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54632</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53834</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60527</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.77098</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.83945</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.21204</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1585</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87809</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26214</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16637</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32517</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10654</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15106</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70987</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04205</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89397</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05248</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.96109</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07374</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87836</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44699</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8142699999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8345399999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44097</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48275</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46736</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17714</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25067</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27168</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15958</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49346</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.48803</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.5840299999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66572</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63179</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8966900000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.58826</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7014600000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7782100000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8659600000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52247</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7779299999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72234</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64483</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63698</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.58627</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50339</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5114</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57753</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57994</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.60136</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23523</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51074</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57763</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.7181900000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71745</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.8595900000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45608</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59696</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54992</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60162</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72938</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56276</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8724500000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6980299999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57855</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51476</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64664</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34162</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51383</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49148</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.01229</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59257</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49092</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49359</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.65127</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4829</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45592</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5339400000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.66008</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51634</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.71297</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55737</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5216000000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.48057</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30977</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24457</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14557</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.23834</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.18903</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22365</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08583</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18094</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.14631</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33004</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24515</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21163</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.09445000000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27415</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10341</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20887</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19442</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.19699</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06123</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32324</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30138</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45253</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78496</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87109</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.7074400000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5917899999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44878</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41171</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5599500000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65146</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8696499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.49334</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.69539</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.45154</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83411</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48957</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.57737</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33493</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.90455</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23791</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24277</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.40404</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38461</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08569</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65388</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.74285</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46684</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24472</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25507</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48404</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.66713</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27329</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27912</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22298</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21331</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25617</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20502</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20551</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.09247</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22439</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.09345999999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24888</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22048</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15727</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20244</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23818</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24157</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22186</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22492</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24146</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24905</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22003</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24026</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30681</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27179</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32604</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22203</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.74693</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5525800000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.53227</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5704600000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48882</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.66469</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.83861</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.57641</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.54165</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.49417</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.67075</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.50361</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.5153099999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.53596</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.55903</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.69547</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.51305</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48878</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.74863</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49056</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.15091</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24825</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.25369</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24589</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24293</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24795</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25793</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22457</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.26087</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27755</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33086</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.12476</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63979</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.84094</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31465</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.49111</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.44916</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.62983</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.56771</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6977899999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6553099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.72961</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84866</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6872200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.58708</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.54125</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.53462</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33141</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.43181</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47835</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47299</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5037200000000001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.61222</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6196499999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68725</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86949</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40881</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5301699999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75462</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60673</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65374</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37377</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13964</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.13653</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46527</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.4656</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24128</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25297</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23344</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26362</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26401</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13944</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.13016</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.12346</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22791</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22826</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.23183</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.11907</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.10284</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23271</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.21198</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.09431999999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11391</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27422</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24747</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25028</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28479</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25504</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.26802</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24531</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.23043</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22941</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27081</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.15037</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23633</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.10084</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10939</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.10763</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.10763</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10868</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09883</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.10763</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.10091</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.10081</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.11209</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.07214</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14188</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01597</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02932</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00085</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03842</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02207</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19988</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.11053</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.29956</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5284099999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23392</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23897</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23549</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11465</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21631</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11855</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09777</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10806</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.12224</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08744</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.13357</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.14028</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27216</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10766</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5627000000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86771</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8589</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10719</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09936</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16287</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.12812</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.08916</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6605800000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59797</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.07633</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97327</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.5667300000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.7247100000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.61325</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83014</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82836</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8326399999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9303400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.55567</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6092799999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33421</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43851</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48211</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23787</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25346</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.23062</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23407</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.11477</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25657</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.57031</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49426</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32336</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.71157</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46101</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.54052</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46931</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.73761</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8508300000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.1378</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48801</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5673899999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5750599999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.04694</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8869199999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.54011</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6489</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.49177</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.46539</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22429</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3412</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.59438</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.2647</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.03561</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.65454</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.8834</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5213300000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.6511399999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5840299999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.80776</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.74571</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98817</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89055</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.80237</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72809</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34565</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.47533</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.49659</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.7902</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21663</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.57499</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.7941699999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.41839</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.49079</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.45221</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5338200000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67198</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.65865</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47829</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35159</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.91583</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52903</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.49475</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50296</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.48001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50798</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5077900000000001</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.58839</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.46236</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35212</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14549</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19826</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12087</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22495</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14759</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14398</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19216</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15195</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19598</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43498</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37929</v>
       </c>
     </row>
   </sheetData>
